--- a/Tables/pairwise_adonis_same_sheet_April.xlsx
+++ b/Tables/pairwise_adonis_same_sheet_April.xlsx
@@ -467,10 +467,10 @@
         <v>36.828788533162</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0027</v>
+        <v>0.0024</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0108</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="3">
@@ -505,10 +505,10 @@
         <v>32.970943972416</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003</v>
+        <v>0.0017</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0108</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="4">
@@ -543,10 +543,10 @@
         <v>4.60216487502448</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0108</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="5">
@@ -581,10 +581,10 @@
         <v>3.68577680478179</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0069</v>
+        <v>0.0056</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0108</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="6">
@@ -619,10 +619,10 @@
         <v>14.834579997116</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0018</v>
+        <v>0.0021</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0108</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="7">
@@ -657,10 +657,10 @@
         <v>12.5020995366175</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0108</v>
+        <v>0.0102</v>
       </c>
     </row>
   </sheetData>
